--- a/public/templates/examples/A-027-CybersecurityBudgetResourceAllocationRecord-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-027-CybersecurityBudgetResourceAllocationRecord-EXAMPLE-L.xlsx
@@ -521,7 +521,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>SAMPLE — illustrative record, not an adopted document</t>
+          <t>SAMPLE: illustrative record, not an adopted document</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Indiana statutes and administrative code: IC 36-8-16.7 — allowable uses of statewide 911 fund distributions</t>
+          <t>Indiana statutes and administrative code: IC 36-8-16.7: allowable uses of statewide 911 fund distributions</t>
         </is>
       </c>
     </row>

--- a/public/templates/examples/A-027-CybersecurityBudgetResourceAllocationRecord-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-027-CybersecurityBudgetResourceAllocationRecord-EXAMPLE-L.xlsx
@@ -18,7 +18,7 @@
   <numFmts count="0"/>
   <fonts count="8">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
@@ -294,7 +294,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="666750" cy="666750"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -361,12 +361,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>

--- a/public/templates/examples/A-027-CybersecurityBudgetResourceAllocationRecord-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-027-CybersecurityBudgetResourceAllocationRecord-EXAMPLE-L.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ledger" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Ledger!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -589,7 +592,7 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="16" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Coverage / Cycle</t>
@@ -615,7 +618,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="8" t="n"/>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -647,7 +650,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>0001</t>
@@ -679,7 +682,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>0002</t>
@@ -711,7 +714,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>0003</t>
@@ -743,7 +746,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>0004</t>
@@ -775,7 +778,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>0005</t>
@@ -807,7 +810,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>0006</t>
@@ -839,7 +842,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="34.7" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>0007</t>
@@ -871,7 +874,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="34.7" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>0008</t>
@@ -929,7 +932,7 @@
     <row r="24" ht="29.75" customHeight="1">
       <c r="A24" s="8" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25" ht="50.5" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>FY2026 commits about $235,000 across the part-time Information Security Analyst, 24x7 managed detection, SIEM, enterprise endpoint and email security, NG911 security integration, penetration testing, training for 38 staff, and dual-center backup and DR. Tied to the Cybersecurity Charter. Two lines draw on the state 911 fund under IC 36-8-16.7; the rest is the agency operating budget.</t>
@@ -967,7 +970,7 @@
       <c r="E28" s="12" t="n"/>
       <c r="F28" s="12" t="n"/>
     </row>
-    <row r="29" ht="34" customHeight="1">
+    <row r="29" ht="82.2" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Prepared by (Information Security Analyst)</t>
@@ -991,7 +994,7 @@
       <c r="E29" s="13" t="n"/>
       <c r="F29" s="13" t="n"/>
     </row>
-    <row r="30" ht="51" customHeight="1">
+    <row r="30" ht="66.4" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Approved by (Executive Director)</t>
@@ -1121,11 +1124,11 @@
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="2" t="n"/>
+    <row r="48">
+      <c r="A48"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A27:F27"/>
@@ -1148,7 +1151,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A4:B4"/>
@@ -1157,7 +1159,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;36 &amp;KBFBFBFSAMPLE</oddHeader>
     <oddFooter/>
